--- a/4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl/test-results/page-level-excels/oocihm.N_00155_18750610/oocihm.N_00155_18750610.3.xlsx
+++ b/4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl/test-results/page-level-excels/oocihm.N_00155_18750610/oocihm.N_00155_18750610.3.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="oocihm.N_00155_18750610.3" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="oocihm.N_00155_18750610.3" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -464,12 +464,12 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - paddle</t>
+          <t>Possible duplicate lines - paddle</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - abbyy</t>
+          <t>Possible duplicate lines - abbyy</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -581,19 +581,15 @@
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.N_00155_18750610\oocihm.N_00155_18750610.3.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.N_00155_18750610\oocihm.N_00155_18750610.3.txt</t>
         </is>
       </c>
       <c r="C2" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.N_00155_18750610\oocihm.N_00155_18750610.3.txt</t>
-        </is>
-      </c>
-      <c r="D2" s="1" t="inlineStr">
-        <is>
-          <t>L427: possible duplicated/overlap line with previous line (similarity 84%) :: Hon. Mr. Vail, Minister of Militia, will re-</t>
-        </is>
-      </c>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.N_00155_18750610\oocihm.N_00155_18750610.3.txt</t>
+        </is>
+      </c>
+      <c r="D2" s="1" t="inlineStr"/>
       <c r="E2" s="1" t="inlineStr"/>
       <c r="F2" s="1" t="inlineStr">
         <is>
@@ -684,11 +680,7 @@
           <t>2797</t>
         </is>
       </c>
-      <c r="D3" s="1" t="inlineStr">
-        <is>
-          <t>L663: suspicious token(s): 114c (letter/digit mix) | possible duplicated/overlap line with previous line (similarity 72%) :: S. R.- lc. for cash; nominally 114c. for July;</t>
-        </is>
-      </c>
+      <c r="D3" s="1" t="inlineStr"/>
       <c r="E3" s="1" t="inlineStr"/>
       <c r="F3" s="1" t="inlineStr"/>
       <c r="G3" s="1" t="inlineStr"/>
@@ -771,11 +763,7 @@
           <t>13375</t>
         </is>
       </c>
-      <c r="D4" s="1" t="inlineStr">
-        <is>
-          <t>L878: possible duplicated/overlap line with previous line (similarity 77%) :: It is expected that there will be brigade</t>
-        </is>
-      </c>
+      <c r="D4" s="1" t="inlineStr"/>
       <c r="E4" s="1" t="inlineStr"/>
       <c r="F4" s="1" t="inlineStr"/>
       <c r="G4" s="1" t="inlineStr"/>
@@ -846,7 +834,7 @@
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
-          <t>121</t>
+          <t>119</t>
         </is>
       </c>
       <c r="C5" s="1" t="inlineStr">
@@ -999,12 +987,12 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap issue count</t>
+          <t>Possible duplicate lines issue count</t>
         </is>
       </c>
       <c r="B7" s="1" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C7" s="1" t="inlineStr">
@@ -2698,7 +2686,7 @@
       <c r="G35" s="1" t="inlineStr"/>
       <c r="H35" s="1" t="inlineStr">
         <is>
-          <t>L663: suspicious token(s): 114c (letter/digit mix) | possible duplicated/overlap line with previous line (similarity 72%) :: S. R.- lc. for cash; nominally 114c. for July;</t>
+          <t>L663: suspicious token(s): 114c (letter/digit mix) :: S. R.- lc. for cash; nominally 114c. for July;</t>
         </is>
       </c>
       <c r="I35" s="1" t="inlineStr">
